--- a/docs/skippy-data-bundle.xlsx
+++ b/docs/skippy-data-bundle.xlsx
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
-        <v>56.8</v>
+        <v>59.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H3" t="n">
-        <v>60.6</v>
+        <v>63.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
         <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H4" t="n">
-        <v>68.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         <v>89</v>
       </c>
       <c r="G5" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H5" t="n">
-        <v>67.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
         <v>94</v>
       </c>
       <c r="G6" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H6" t="n">
-        <v>71.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1743,13 +1743,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>58.3</v>
+        <v>54.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H8" t="n">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1820,10 +1820,10 @@
         <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H9" t="n">
-        <v>31.8</v>
+        <v>33.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
         <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H10" t="n">
-        <v>60.6</v>
+        <v>63.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         <v>83</v>
       </c>
       <c r="G11" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H11" t="n">
-        <v>62.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1931,10 +1931,10 @@
         <v>75</v>
       </c>
       <c r="G12" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H12" t="n">
-        <v>56.8</v>
+        <v>59.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H13" t="n">
-        <v>72.7</v>
+        <v>76.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         <v>84</v>
       </c>
       <c r="G14" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H14" t="n">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
         <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H15" t="n">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         <v>99</v>
       </c>
       <c r="G16" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H16" t="n">
-        <v>75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         <v>94</v>
       </c>
       <c r="G17" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H17" t="n">
-        <v>71.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>77</v>
       </c>
       <c r="G18" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H18" t="n">
-        <v>58.3</v>
+        <v>61.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         <v>93</v>
       </c>
       <c r="G19" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H19" t="n">
-        <v>70.5</v>
+        <v>73.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
         <v>83</v>
       </c>
       <c r="G20" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H20" t="n">
-        <v>62.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2264,10 +2264,10 @@
         <v>89</v>
       </c>
       <c r="G21" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H21" t="n">
-        <v>67.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>81</v>
       </c>
       <c r="G22" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H22" t="n">
-        <v>61.4</v>
+        <v>64.3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         <v>82</v>
       </c>
       <c r="G23" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H23" t="n">
-        <v>62.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
         <v>84</v>
       </c>
       <c r="G24" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H24" t="n">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2409,13 +2409,13 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="H25" t="n">
-        <v>58.3</v>
+        <v>54.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2446,13 +2446,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="H26" t="n">
-        <v>58.3</v>
+        <v>54.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
         <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H27" t="n">
-        <v>30.3</v>
+        <v>31.8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>90</v>
       </c>
       <c r="G28" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H28" t="n">
-        <v>68.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         <v>90</v>
       </c>
       <c r="G29" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H29" t="n">
-        <v>68.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
         <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="H30" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2631,13 +2631,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="H31" t="n">
-        <v>58.3</v>
+        <v>54.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         <v>91</v>
       </c>
       <c r="G32" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H32" t="n">
-        <v>68.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
         <v>91</v>
       </c>
       <c r="G33" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H33" t="n">
-        <v>68.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         <v>48</v>
       </c>
       <c r="G34" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H34" t="n">
-        <v>36.4</v>
+        <v>38.1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2779,13 +2779,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G35" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="H35" t="n">
-        <v>58.3</v>
+        <v>54.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2816,13 +2816,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G36" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="H36" t="n">
-        <v>52.8</v>
+        <v>48.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12374,270 +12374,287 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Eval prompt set</t>
+          <t>Methodology version</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v2 (eval/prompts_v2.json)</t>
+          <t>2026-05-08-post-remediation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>44 prompts × 3 samples = 132 substring-graded scores per run.</t>
+          <t>Bumped after SK-P0-001 (persona quarantined). See eval/EVAL_SET_CHANGELOG.md.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Eval prompt set</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10 (9 in some legacy entries)</t>
+          <t>v2 (eval/prompts_v2.json)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>coding, general, multihop, numerical_precision, persona, rag_blog, rag_datasheet, rag_email, reasoning, refusal.</t>
+          <t>42 active prompts × 3 samples = 126 substring-graded scores per run. (Was 44 × 3 = 132 pre-2026-05-08; persona×2 quarantined as BROKEN_SUBSTRING_INCOMPATIBLE.)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grading method</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Substring matching</t>
+          <t>9 active + 1 broken-quarantined</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Each prompt has a list of gold substrings; case-insensitive; match_mode='all' = every substring must appear.</t>
+          <t>Active: coding, general, multihop, numerical_precision, rag_blog, rag_datasheet, rag_email, reasoning, refusal. Quarantined: persona (substring grader can't capture; voice metric tool measures it instead).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RAG configuration</t>
+          <t>Grading method</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hybrid retrieval, top-k</t>
+          <t>Substring matching</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ChromaDB semantic + BM25 + cross-encoder reranker; top-k chunks injected into prompt.</t>
+          <t>Each prompt has a list of gold substrings; case-insensitive; match_mode='all' = every substring must appear.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RAG corpus</t>
+          <t>RAG configuration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>61K+ documents</t>
+          <t>Hybrid retrieval, top-k</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>i.MX datasheets (NXP), email archive, blog posts, code, internal notes.</t>
+          <t>ChromaDB semantic + BM25 + cross-encoder reranker; top-k chunks injected into prompt.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Inference hardware</t>
+          <t>RAG corpus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RTX 5090 (32GB)</t>
+          <t>61K+ documents</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Local llama-cpp-python, n_ctx=16384, all eval runs.</t>
+          <t>i.MX datasheets (NXP), email archive, blog posts, code, internal notes.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quantization</t>
+          <t>Inference hardware</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q4_K_M GGUF</t>
+          <t>RTX 5090 (32GB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Same quant across all candidates for apples-to-apples comparison.</t>
+          <t>Local llama-cpp-python, n_ctx=16384, all eval runs.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Training hardware (dense)</t>
+          <t>Quantization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>Q4_K_M GGUF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7B + 14B QLoRA fit; 32B requires H100 cloud rental ($25-35/run).</t>
+          <t>Same quant across all candidates for apples-to-apples comparison.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Training hardware (MoE)</t>
+          <t>Training hardware (dense)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H100 SXM 80GB</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qwen3-30B-A3B QLoRA needed cloud ($15-25/run, ~5 hours).</t>
+          <t>7B + 14B QLoRA fit; 32B requires H100 cloud rental ($25-35/run).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Training cost total</t>
+          <t>Training hardware (MoE)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>~$140 cloud + 4.9 free local hr</t>
+          <t>H100 SXM 80GB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Across all 6+ fine-tune iterations of the v4 campaign.</t>
+          <t>Qwen3-30B-A3B QLoRA needed cloud ($15-25/run, ~5 hours).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Voice gate (separate)</t>
+          <t>Training cost total</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eval/voice_metrics.py</t>
+          <t>~$140 cloud + 4.9 free local hr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Length, bullets/resp, bolds/resp, emojis/resp, boilerplate opener rate.</t>
+          <t>Across all 6+ fine-tune iterations of the v4 campaign.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Safety gate</t>
+          <t>Voice gate (separate)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>made_up_peripheral probe</t>
+          <t>eval/voice_metrics.py</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adversarial prompts about fictional features; pass = correct refusal.</t>
+          <t>Length, bullets/resp, bolds/resp, emojis/resp, boilerplate opener rate.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Schema versioning gotcha</t>
+          <t>Safety gate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>general n=3 vs n=6</t>
+          <t>made_up_peripheral probe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prompt set was extended mid-campaign; legacy entries have general/3 samples, newer have general/6. Δ-vs-base on raw counts is unaffected; per-category rates may not be directly comparable across eval-set versions.</t>
+          <t>Adversarial prompts about fictional features; pass = correct refusal.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Eval source repo</t>
+          <t>Schema versioning gotcha</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>personal-ai-framework</t>
+          <t>general n=3 vs n=6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://github.com/&lt;user&gt;/personal-ai-framework — eval/run_accuracy_eval.py + eval/compare_accuracy_runs.py.</t>
+          <t>Prompt set was extended mid-campaign; legacy entries have general/3 samples, newer have general/6. Δ-vs-base on raw counts is unaffected; per-category rates may not be directly comparable across eval-set versions.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Recipe taxonomy doc</t>
+          <t>Eval source repo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>docs/recipe-taxonomy.md</t>
+          <t>personal-ai-framework</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8-dimensional tuple framework. Two recipes that match on all 8 dims should produce the same outcome.</t>
+          <t>https://github.com/&lt;user&gt;/personal-ai-framework — eval/run_accuracy_eval.py + eval/compare_accuracy_runs.py.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Recipe taxonomy doc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>docs/recipe-taxonomy.md</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8-dimensional tuple framework. Two recipes that match on all 8 dims should produce the same outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>White paper</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>docs/skippy-white-paper.md</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Full narrative: iteration arc, gotchas, verification framework, cost arc, recommendations, cross-family + Mistral falsification, recipe taxonomy refs.</t>
         </is>

--- a/docs/skippy-data-bundle.xlsx
+++ b/docs/skippy-data-bundle.xlsx
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RTX 5090 throughput measurements (decode tok/s, prefill, RAG total).</t>
+          <t>RTX 5090 throughput measurements (decode tok/s, prefill, RAG total). Vendored from keyhole canonical anchor file; see methodology.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11697,27 +11697,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Qwen 2.5 7B Q4_K_M</t>
+          <t>Llama-3.1 8B Q4_K_M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.68</v>
+        <v>4.92</v>
       </c>
       <c r="C2" t="n">
-        <v>10865</v>
+        <v>10162</v>
       </c>
       <c r="D2" t="n">
-        <v>211.7</v>
+        <v>211.5</v>
       </c>
       <c r="E2" t="n">
-        <v>183.9</v>
+        <v>171</v>
       </c>
       <c r="F2" t="n">
-        <v>12.3</v>
+        <v>13.33</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>anchor: qwen2.5-7b-dense</t>
+          <t>anchor: llama_3_1_8b_dense</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
         <v>182.7</v>
       </c>
       <c r="F3" t="n">
-        <v>12.6</v>
+        <v>12.56</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -11751,34 +11751,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Llama-3.1 8B Q4_K_M</t>
+          <t>Qwen 2.5 32B Q4_K_M</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.92</v>
+        <v>19.85</v>
       </c>
       <c r="C4" t="n">
-        <v>10162</v>
+        <v>2855</v>
       </c>
       <c r="D4" t="n">
-        <v>211.5</v>
+        <v>62.4</v>
       </c>
       <c r="E4" t="n">
-        <v>171</v>
+        <v>52.7</v>
       </c>
       <c r="F4" t="n">
-        <v>13.3</v>
+        <v>43.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>anchor: llama_3_1_8b_dense</t>
+          <t>anchor: qwen_2_5_32b_dense</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skippy 7B v4 (= Qwen 7B alias)</t>
+          <t>Qwen 2.5 7B Q4_K_M</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -11794,38 +11794,92 @@
         <v>183.9</v>
       </c>
       <c r="F5" t="n">
-        <v>12.3</v>
+        <v>12.27</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FT preserves base GGUF size + compute graph</t>
+          <t>anchor: qwen_2_5_7b_dense</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Skippy Mistral v4 (= Mistral alias)</t>
+          <t>Qwen 3 30B-A3B (MoE) Q4_K_M</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6228</v>
+      </c>
+      <c r="D6" t="n">
+        <v>249.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>159</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>anchor: skippy_moe_30b_a3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Skippy 7B v4 (= qwen_2_5_7b_dense alias)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10865</v>
+      </c>
+      <c r="D7" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FT preserves base GGUF size + compute graph (alias: qwen_2_5_7b_dense)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Skippy Mistral v4 (= mistral_7b_v03_dense alias)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>4.37</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>10217</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D8" t="n">
         <v>239.4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E8" t="n">
         <v>182.7</v>
       </c>
-      <c r="F6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>FT preserves base GGUF size + compute graph</t>
+      <c r="F8" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FT preserves base GGUF size + compute graph (alias: mistral_7b_v03_dense)</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12660,6 +12714,23 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>perf_5090 source</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>keyhole-canonical (vendored)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>vendored from keyhole/data/output/llm_anchors_5090.json (git_head 5911f2d07970, methodology 2026-05-08-post-remediation)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
